--- a/5/search/strategy_visualization/drone_summary.xlsx
+++ b/5/search/strategy_visualization/drone_summary.xlsx
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>278.2</v>
+        <v>292.8</v>
       </c>
       <c r="C3" t="n">
-        <v>139.5</v>
+        <v>127.6</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -504,17 +504,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>87.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="C4" t="n">
-        <v>131.3</v>
+        <v>125.8</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>M3, M1</t>
+          <t>M1</t>
         </is>
       </c>
     </row>
@@ -525,10 +525,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>292</v>
+        <v>295.4</v>
       </c>
       <c r="C5" t="n">
-        <v>122.7</v>
+        <v>105.8</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>116.2</v>
+        <v>118</v>
       </c>
       <c r="C6" t="n">
-        <v>138</v>
+        <v>135.4</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>

--- a/5/search/strategy_visualization/drone_summary.xlsx
+++ b/5/search/strategy_visualization/drone_summary.xlsx
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>292.8</v>
+        <v>278.2</v>
       </c>
       <c r="C3" t="n">
-        <v>127.6</v>
+        <v>139.4</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -504,17 +504,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>82</v>
+        <v>82.3</v>
       </c>
       <c r="C4" t="n">
-        <v>125.8</v>
+        <v>135.4</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
     </row>
